--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:00:17+00:00</t>
+    <t>2025-02-04T09:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1105,7 +1105,7 @@
     <t>Practitioner.identifier:idNatPs.value</t>
   </si>
   <si>
-    <t>Identifiant national unique du PS. Il est préfixé par un chiffre, par ex. 8 + RPPS. Cet identifiant ne doit pas être construit, la donnée peut être trouvée dans l'annuaire santé ou dans la carte CPx.</t>
+    <t>Identifiant national unique du PS. Il est préfixé par un chiffre, par ex. 8 + RPPS. Cet identifiant ne doit pas être construit, la donnée peut être trouvée dans l'annuaire santé, sur ProSantéConnect ou dans la carte CPx.</t>
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.period</t>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:12:17+00:00</t>
+    <t>2025-02-04T10:05:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1105,7 +1105,7 @@
     <t>Practitioner.identifier:idNatPs.value</t>
   </si>
   <si>
-    <t>Identifiant national unique du PS. Il est préfixé par un chiffre, par ex. 8 + RPPS. Cet identifiant ne doit pas être construit, la donnée peut être trouvée dans l'annuaire santé, sur ProSantéConnect ou dans la carte CPx.</t>
+    <t>Identifiant national unique du PS. Cet identifiant ne doit pas être construit, la donnée peut être trouvée dans l'annuaire santé, sur ProSantéConnect ou dans la carte CPx. Pour plus d'informations, cf Annexe Transverse – Source des données métier pour les professionnels et les structures du CI-SIS.</t>
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.period</t>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T10:05:16+00:00</t>
+    <t>2025-02-04T10:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1060,7 +1060,7 @@
     <t>idNatPs</t>
   </si>
   <si>
-    <t>Identifiant national unique des PS. Cet identifiant est notamment utilisé dans le cadre du DMP et de la CPS. Cet identifiant est préfixé selon source de provenance de l'identifiant (cf Annexe Transverse – Source des données métier pour les professionnels et les structures du CI-SIS.)</t>
+    <t>Identifiant national unique du professionnel de santé</t>
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.id</t>
@@ -1073,10 +1073,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.type</t>
-  </si>
-  <si>
-    <t>Type d’identifiant national du PS,
-Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les préfixes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1106,6 +1102,9 @@
   </si>
   <si>
     <t>Identifiant national unique du PS. Cet identifiant ne doit pas être construit, la donnée peut être trouvée dans l'annuaire santé, sur ProSantéConnect ou dans la carte CPx. Pour plus d'informations, cf Annexe Transverse – Source des données métier pour les professionnels et les structures du CI-SIS.</t>
+  </si>
+  <si>
+    <t>Cet identifiant est préfixé selon source de provenance de l'identifiant. Ces préfixes (1, 3, 4, 5, 6) proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne.</t>
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.period</t>
@@ -7093,7 +7092,7 @@
         <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>233</v>
       </c>
       <c r="M45" t="s" s="2">
         <v>234</v>
@@ -7112,7 +7111,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -7130,10 +7129,10 @@
         <v>151</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7180,7 +7179,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>299</v>
@@ -7212,7 +7211,7 @@
         <v>300</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>302</v>
@@ -7228,7 +7227,7 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>304</v>
@@ -7296,7 +7295,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>309</v>
@@ -7325,10 +7324,10 @@
         <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>312</v>
@@ -8160,10 +8159,10 @@
         <v>151</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8242,7 +8241,7 @@
         <v>300</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>302</v>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T10:10:21+00:00</t>
+    <t>2025-02-04T14:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -763,194 +763,13 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>Practitioner.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
     <t>Practitioner.identifier.system</t>
   </si>
   <si>
     <t>The namespace for the identifier value</t>
   </si>
   <si>
-    <t>Establishes the namespace for the value - that is, a OID that describes a set values that are unique.
-the namespace for the practitioner identifier value is fixed in France.
-Pour un PS identifié à partir de sa carte CPS, OID = 1.2.250.1.71.4.2.1
-Pour un employé identifié au sein de sa structure, OID de l'établissement, branche de gestion des employés ou http://hopitalTest.fr/fhir/namingsystem/employes</t>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -1092,9 +911,6 @@
     <t>Practitioner.identifier:idNatPs.system</t>
   </si>
   <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
     <t>urn:oid:1.2.250.1.71.4.2.1</t>
   </si>
   <si>
@@ -1158,6 +974,10 @@
   </si>
   <si>
     <t>Practitioner.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
   </si>
   <si>
     <t>Whether this practitioner's record is in active use</t>
@@ -1502,9 +1322,30 @@
     <t>Practitioner.qualification.code.coding</t>
   </si>
   <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
     <t>closed</t>
   </si>
   <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
     <t>Practitioner.qualification:degree.code.coding:degreeType</t>
   </si>
   <si>
@@ -1524,6 +1365,27 @@
   </si>
   <si>
     <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.period</t>
@@ -1993,11 +1855,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN116"/>
+  <dimension ref="A1:AN105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.38671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.70703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.15625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2015,7 +1877,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="45.10546875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -4914,19 +4776,23 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4938,7 +4804,7 @@
         <v>78</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>78</v>
@@ -4974,7 +4840,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>106</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4986,16 +4852,16 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -5003,21 +4869,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -5026,19 +4892,19 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>111</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>112</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>113</v>
+        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5052,7 +4918,7 @@
         <v>78</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>78</v>
@@ -5076,40 +4942,40 @@
         <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>117</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5117,10 +4983,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5131,7 +4997,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5143,20 +5009,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5204,13 +5066,13 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
@@ -5219,13 +5081,13 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5233,10 +5095,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5256,18 +5118,20 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>103</v>
+        <v>268</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>104</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5316,7 +5180,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>106</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5328,16 +5192,16 @@
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5345,21 +5209,23 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -5368,21 +5234,21 @@
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>111</v>
+        <v>278</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5418,19 +5284,19 @@
         <v>78</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>117</v>
+        <v>208</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5442,27 +5308,27 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>107</v>
+        <v>216</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5482,23 +5348,19 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5510,7 +5372,7 @@
         <v>78</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>78</v>
@@ -5546,7 +5408,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5558,13 +5420,13 @@
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>260</v>
+        <v>107</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5575,21 +5437,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
@@ -5598,19 +5460,19 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
+        <v>112</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>264</v>
+        <v>113</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5648,37 +5510,37 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5689,10 +5551,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5709,7 +5571,7 @@
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>90</v>
@@ -5718,14 +5580,16 @@
         <v>169</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5750,13 +5614,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5774,7 +5638,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5789,10 +5653,10 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>273</v>
+        <v>192</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -5803,10 +5667,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5814,7 +5678,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -5829,17 +5693,19 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5849,7 +5715,7 @@
         <v>78</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>78</v>
@@ -5864,13 +5730,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5888,7 +5754,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5903,10 +5769,10 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -5917,10 +5783,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>240</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5928,7 +5794,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -5943,19 +5809,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>283</v>
+        <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>241</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5965,10 +5831,10 @@
         <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>78</v>
@@ -6004,7 +5870,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6019,13 +5885,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6033,10 +5899,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6044,7 +5910,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
@@ -6062,17 +5928,15 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6084,7 +5948,7 @@
         <v>78</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>78</v>
@@ -6120,7 +5984,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6135,13 +5999,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6149,10 +6013,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6175,20 +6039,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6200,7 +6060,7 @@
         <v>78</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>78</v>
@@ -6236,7 +6096,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6251,13 +6111,13 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6265,10 +6125,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6291,16 +6151,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6314,7 +6174,7 @@
         <v>78</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>78</v>
@@ -6350,7 +6210,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6365,13 +6225,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6379,12 +6239,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6393,7 +6255,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6405,16 +6267,18 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>211</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6462,13 +6326,13 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>208</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>78</v>
@@ -6477,24 +6341,24 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>323</v>
+        <v>215</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>324</v>
+        <v>216</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>325</v>
+        <v>217</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>326</v>
+        <v>219</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6514,20 +6378,18 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>327</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6576,7 +6438,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>106</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6588,16 +6450,16 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6605,23 +6467,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -6630,21 +6490,21 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6680,19 +6540,19 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6704,27 +6564,27 @@
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>216</v>
+        <v>107</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6741,22 +6601,26 @@
         <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6780,13 +6644,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6804,7 +6668,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>106</v>
+        <v>229</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6816,13 +6680,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6833,21 +6697,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6856,21 +6720,23 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>111</v>
+        <v>233</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6879,7 +6745,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -6894,49 +6760,49 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>117</v>
+        <v>238</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6947,10 +6813,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>301</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6958,7 +6824,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6967,25 +6833,25 @@
         <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6995,10 +6861,10 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>78</v>
@@ -7010,13 +6876,13 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7034,7 +6900,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7049,13 +6915,13 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7063,10 +6929,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7089,20 +6955,18 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7111,10 +6975,10 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>78</v>
@@ -7126,13 +6990,13 @@
         <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7150,7 +7014,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7165,13 +7029,13 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7179,10 +7043,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7190,7 +7054,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -7205,20 +7069,16 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7227,10 +7087,10 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>78</v>
@@ -7266,7 +7126,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7281,13 +7141,13 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7295,10 +7155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>305</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7306,7 +7166,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -7321,16 +7181,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>268</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>349</v>
+        <v>269</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>350</v>
+        <v>270</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7344,7 +7204,7 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>78</v>
@@ -7380,7 +7240,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7395,13 +7255,13 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7409,10 +7269,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7435,20 +7295,26 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q48" s="2"/>
+      <c r="Q48" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="R48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7492,7 +7358,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7507,24 +7373,24 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>323</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>78</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7535,7 +7401,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
@@ -7547,18 +7413,20 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7606,13 +7474,13 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>78</v>
@@ -7621,13 +7489,13 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7635,14 +7503,12 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7663,17 +7529,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>325</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>212</v>
+        <v>329</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7722,7 +7590,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7737,24 +7605,24 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>215</v>
+        <v>330</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>216</v>
+        <v>331</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>217</v>
+        <v>332</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>219</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7765,7 +7633,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>78</v>
@@ -7774,19 +7642,23 @@
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>334</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>104</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7834,28 +7706,28 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>107</v>
+        <v>340</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7863,21 +7735,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7886,21 +7758,21 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>111</v>
+        <v>343</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7924,52 +7796,52 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>78</v>
+        <v>347</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>117</v>
+        <v>342</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>107</v>
+        <v>349</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7977,10 +7849,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7997,25 +7869,23 @@
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>169</v>
+        <v>352</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>225</v>
+        <v>355</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8040,13 +7910,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8064,7 +7934,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>229</v>
+        <v>351</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8079,13 +7949,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>192</v>
+        <v>356</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>230</v>
+        <v>357</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>358</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8096,7 +7966,7 @@
         <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>231</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8104,10 +7974,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -8116,22 +7986,20 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>232</v>
+        <v>360</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>233</v>
+        <v>361</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8141,7 +8009,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>360</v>
+        <v>78</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8156,13 +8024,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8180,13 +8048,13 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
@@ -8195,13 +8063,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>230</v>
+        <v>364</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8209,10 +8077,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8220,10 +8088,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
@@ -8232,23 +8100,19 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>368</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8257,10 +8121,10 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8284,25 +8148,23 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
@@ -8311,13 +8173,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>306</v>
+        <v>371</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>308</v>
+        <v>373</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8325,10 +8187,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>309</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8336,7 +8198,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -8348,20 +8210,18 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>310</v>
+        <v>104</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8374,7 +8234,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8410,7 +8270,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>106</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8422,16 +8282,16 @@
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>315</v>
+        <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>316</v>
+        <v>107</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8439,21 +8299,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
@@ -8462,18 +8322,20 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>319</v>
+        <v>110</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>320</v>
+        <v>111</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8522,28 +8384,28 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>322</v>
+        <v>117</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>323</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8551,44 +8413,46 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>326</v>
+        <v>376</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>327</v>
+        <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>328</v>
+        <v>378</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8636,28 +8500,28 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8665,10 +8529,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8679,7 +8543,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8688,29 +8552,25 @@
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>283</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q59" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8754,13 +8614,13 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -8772,21 +8632,21 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8794,10 +8654,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8806,23 +8666,19 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>375</v>
+        <v>232</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8846,13 +8702,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8870,13 +8726,13 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
@@ -8885,13 +8741,13 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8899,10 +8755,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8913,7 +8769,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -8922,22 +8778,20 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>384</v>
+        <v>260</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8986,13 +8840,13 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
@@ -9001,13 +8855,13 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9015,10 +8869,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9029,7 +8883,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9038,23 +8892,19 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>393</v>
+        <v>268</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9102,13 +8952,13 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
@@ -9117,13 +8967,13 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>398</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9131,12 +8981,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9145,7 +8997,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9154,21 +9006,19 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>169</v>
+        <v>367</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9192,13 +9042,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9216,13 +9066,13 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
@@ -9231,13 +9081,13 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9245,10 +9095,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9268,21 +9118,19 @@
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>411</v>
+        <v>103</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>104</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
+        <v>105</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>414</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9330,7 +9178,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>410</v>
+        <v>106</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9342,16 +9190,16 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>416</v>
+        <v>107</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9359,14 +9207,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9385,18 +9233,18 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>419</v>
+        <v>110</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>111</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9444,7 +9292,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>418</v>
+        <v>117</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9456,16 +9304,16 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>423</v>
+        <v>107</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9473,14 +9321,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9493,22 +9341,26 @@
         <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>426</v>
+        <v>110</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>427</v>
+        <v>378</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9544,17 +9396,19 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AC66" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>425</v>
+        <v>380</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9566,16 +9420,16 @@
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>431</v>
+        <v>192</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9583,10 +9437,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9597,7 +9451,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9609,16 +9463,18 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>104</v>
+        <v>382</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>105</v>
+        <v>383</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9666,25 +9522,25 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>106</v>
+        <v>381</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>107</v>
+        <v>385</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9695,21 +9551,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -9721,17 +9577,15 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>111</v>
+        <v>387</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9756,13 +9610,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9780,28 +9634,28 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>117</v>
+        <v>386</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>372</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -9809,46 +9663,42 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>437</v>
+        <v>104</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9896,25 +9746,25 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>439</v>
+        <v>106</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9925,14 +9775,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9951,18 +9801,18 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>111</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -9998,19 +9848,19 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>440</v>
+        <v>117</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10022,13 +9872,13 @@
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>444</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10039,10 +9889,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>414</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10050,10 +9900,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10062,19 +9912,23 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10098,37 +9952,35 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC71" s="2"/>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>78</v>
+        <v>420</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
@@ -10137,13 +9989,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10151,12 +10003,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10174,20 +10028,22 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>319</v>
+        <v>147</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10212,13 +10068,11 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>78</v>
+        <v>426</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10236,13 +10090,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -10251,13 +10105,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10265,12 +10119,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10288,19 +10144,23 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>458</v>
+        <v>416</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10324,13 +10184,11 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>78</v>
+        <v>428</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10348,13 +10206,13 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
@@ -10363,10 +10221,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10377,14 +10235,12 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10393,7 +10249,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10402,19 +10258,23 @@
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10462,13 +10322,13 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
@@ -10477,13 +10337,13 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10491,10 +10351,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>392</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10517,16 +10377,18 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>104</v>
+        <v>393</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10574,7 +10436,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>106</v>
+        <v>392</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10586,16 +10448,16 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>107</v>
+        <v>396</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>78</v>
+        <v>397</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10603,21 +10465,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -10629,17 +10491,15 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>268</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>111</v>
+        <v>399</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10688,25 +10548,25 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>117</v>
+        <v>398</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10717,46 +10577,44 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="D77" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>110</v>
+        <v>367</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10804,7 +10662,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>439</v>
+        <v>366</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10816,16 +10674,16 @@
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10833,10 +10691,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>440</v>
+        <v>374</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10847,7 +10705,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -10859,18 +10717,16 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
+        <v>105</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>443</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
       </c>
@@ -10918,25 +10774,25 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>440</v>
+        <v>106</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>444</v>
+        <v>107</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
@@ -10947,21 +10803,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>445</v>
+        <v>375</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -10973,15 +10829,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>446</v>
+        <v>111</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11006,13 +10864,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11030,28 +10888,28 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>445</v>
+        <v>117</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11059,42 +10917,46 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>470</v>
+        <v>376</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>104</v>
+        <v>378</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -11142,25 +11004,25 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>106</v>
+        <v>380</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11171,14 +11033,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>472</v>
+        <v>381</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11197,18 +11059,18 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11244,19 +11106,19 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>117</v>
+        <v>381</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11268,13 +11130,13 @@
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>107</v>
+        <v>385</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11285,10 +11147,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>386</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11296,10 +11158,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
@@ -11308,23 +11170,19 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>243</v>
+        <v>387</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11348,35 +11206,37 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC82" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>247</v>
+        <v>386</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
@@ -11385,13 +11245,13 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>249</v>
+        <v>372</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11399,14 +11259,12 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11424,23 +11282,19 @@
         <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>243</v>
+        <v>104</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11464,11 +11318,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11486,25 +11342,25 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11515,23 +11371,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11540,23 +11394,21 @@
         <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>244</v>
+        <v>112</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11580,29 +11432,31 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>480</v>
+        <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11614,13 +11468,13 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11631,10 +11485,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>415</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11645,7 +11499,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -11657,19 +11511,19 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>292</v>
+        <v>416</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>293</v>
+        <v>417</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>294</v>
+        <v>418</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>295</v>
+        <v>419</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -11706,25 +11560,23 @@
         <v>78</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>78</v>
+        <v>420</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
@@ -11733,10 +11585,10 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>297</v>
+        <v>422</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>298</v>
+        <v>423</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -11747,12 +11599,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>78</v>
       </c>
@@ -11770,20 +11624,22 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>319</v>
+        <v>147</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -11808,13 +11664,11 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -11832,13 +11686,13 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
@@ -11847,13 +11701,13 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -11861,12 +11715,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
       </c>
@@ -11884,19 +11740,23 @@
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -11920,13 +11780,11 @@
         <v>78</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>78</v>
+        <v>458</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -11944,13 +11802,13 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
@@ -11959,10 +11817,10 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -11973,14 +11831,12 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
@@ -11998,19 +11854,23 @@
         <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>487</v>
+        <v>431</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12058,13 +11918,13 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
@@ -12073,13 +11933,13 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12087,10 +11947,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>433</v>
+        <v>392</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12113,16 +11973,18 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>104</v>
+        <v>393</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12170,7 +12032,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>106</v>
+        <v>392</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12182,16 +12044,16 @@
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>107</v>
+        <v>396</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>78</v>
+        <v>397</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12199,21 +12061,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>489</v>
+        <v>461</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
@@ -12225,17 +12087,15 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>110</v>
+        <v>268</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>111</v>
+        <v>399</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12284,25 +12144,25 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>117</v>
+        <v>398</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12313,14 +12173,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D91" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12333,26 +12195,22 @@
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>110</v>
+        <v>367</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12400,7 +12258,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>439</v>
+        <v>366</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12412,16 +12270,16 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12429,10 +12287,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>440</v>
+        <v>374</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12443,7 +12301,7 @@
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12455,18 +12313,16 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>442</v>
+        <v>105</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>443</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12514,25 +12370,25 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>440</v>
+        <v>106</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>444</v>
+        <v>107</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12543,21 +12399,21 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>445</v>
+        <v>375</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12569,15 +12425,17 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>446</v>
+        <v>111</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12602,13 +12460,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -12626,28 +12484,28 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>445</v>
+        <v>117</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12655,42 +12513,46 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>470</v>
+        <v>376</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>104</v>
+        <v>378</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -12738,25 +12600,25 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>106</v>
+        <v>380</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12767,14 +12629,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>472</v>
+        <v>381</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12793,18 +12655,18 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -12840,19 +12702,19 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>117</v>
+        <v>381</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12864,13 +12726,13 @@
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>107</v>
+        <v>385</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12881,10 +12743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>474</v>
+        <v>386</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12892,10 +12754,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
@@ -12904,23 +12766,19 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>243</v>
+        <v>387</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12944,35 +12802,37 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC96" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>247</v>
+        <v>386</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
@@ -12981,13 +12841,13 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>249</v>
+        <v>372</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -12995,14 +12855,12 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13020,23 +12878,19 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>498</v>
+        <v>104</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13060,11 +12914,13 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -13082,25 +12938,25 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13111,23 +12967,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13136,23 +12990,21 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>502</v>
+        <v>111</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>244</v>
+        <v>112</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13176,29 +13028,31 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13210,13 +13064,13 @@
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13227,10 +13081,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>482</v>
+        <v>415</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13241,7 +13095,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13253,19 +13107,19 @@
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>292</v>
+        <v>416</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>293</v>
+        <v>417</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>294</v>
+        <v>418</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>295</v>
+        <v>419</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13302,25 +13156,23 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>78</v>
+        <v>420</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
@@ -13329,10 +13181,10 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>297</v>
+        <v>422</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>298</v>
+        <v>423</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13343,12 +13195,14 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>78</v>
       </c>
@@ -13366,20 +13220,22 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>319</v>
+        <v>147</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O100" t="s" s="2">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13404,13 +13260,11 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13428,13 +13282,13 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
@@ -13443,13 +13297,13 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13457,12 +13311,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D101" t="s" s="2">
         <v>78</v>
       </c>
@@ -13480,19 +13336,23 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -13516,13 +13376,11 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>78</v>
+        <v>479</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13540,13 +13398,13 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
@@ -13555,10 +13413,10 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13569,14 +13427,12 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13585,7 +13441,7 @@
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -13594,19 +13450,23 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>509</v>
+        <v>431</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13654,13 +13514,13 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
@@ -13669,13 +13529,13 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -13683,10 +13543,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>433</v>
+        <v>392</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13709,16 +13569,18 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>104</v>
+        <v>393</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
       </c>
@@ -13766,7 +13628,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>106</v>
+        <v>392</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13778,16 +13640,16 @@
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>107</v>
+        <v>396</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>78</v>
+        <v>397</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>78</v>
@@ -13795,21 +13657,21 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -13821,17 +13683,15 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>110</v>
+        <v>268</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>111</v>
+        <v>399</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -13880,25 +13740,25 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>117</v>
+        <v>398</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13909,14 +13769,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>435</v>
+        <v>483</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13929,25 +13789,25 @@
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>437</v>
+        <v>484</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>113</v>
+        <v>486</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>206</v>
+        <v>487</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -13972,13 +13832,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -13996,7 +13856,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>439</v>
+        <v>483</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14008,1274 +13868,18 @@
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>192</v>
+        <v>489</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC110" s="2"/>
-      <c r="AD110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="D111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y111" s="2"/>
-      <c r="Z111" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="D112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y112" s="2"/>
-      <c r="Z112" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AN116" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-idnatps-descr/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T14:40:03+00:00</t>
+    <t>2025-02-04T15:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -917,7 +917,7 @@
     <t>Practitioner.identifier:idNatPs.value</t>
   </si>
   <si>
-    <t>Identifiant national unique du PS. Cet identifiant ne doit pas être construit, la donnée peut être trouvée dans l'annuaire santé, sur ProSantéConnect ou dans la carte CPx. Pour plus d'informations, cf Annexe Transverse – Source des données métier pour les professionnels et les structures du CI-SIS.</t>
+    <t>Identifiant national unique du PS. Cet identifiant ne doit être ni construit ni interprété, la donnée peut être trouvée dans l'annuaire santé, sur ProSantéConnect ou dans la carte CPx. Pour plus d'informations, cf Annexe Transverse – Source des données métier pour les professionnels et les structures du CI-SIS.</t>
   </si>
   <si>
     <t>Cet identifiant est préfixé selon source de provenance de l'identifiant. Ces préfixes (1, 3, 4, 5, 6) proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne.</t>
